--- a/.source/Lotto645.xlsx
+++ b/.source/Lotto645.xlsx
@@ -2,27 +2,33 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lotto645" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -50,7 +56,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -414,7 +420,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M1215"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
